--- a/data/trans_orig/IP25B02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27474</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>29490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43590</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159663</t>
+          <t>167141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90546</t>
+          <t>89017</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>146474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161835</t>
+          <t>161836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>272448</t>
+          <t>283155</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>90334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127901</t>
+          <t>128455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122959</t>
+          <t>123827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164276</t>
+          <t>162799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223081</t>
+          <t>222293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282121</t>
+          <t>280651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97763</t>
+          <t>100042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142627</t>
+          <t>141441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115453</t>
+          <t>114959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155075</t>
+          <t>155963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227265</t>
+          <t>229494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>284024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147807</t>
+          <t>149138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102031</t>
+          <t>102603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>139346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>220960</t>
+          <t>221832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275840</t>
+          <t>275049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>42851</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56744</t>
+          <t>56971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>66926</t>
+          <t>65027</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>93984</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>48305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>50595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75587</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>86844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118732</t>
+          <t>118297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>40761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58116</t>
+          <t>58905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41282</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>62535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>88010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116494</t>
+          <t>117369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85490</t>
+          <t>85897</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187612</t>
+          <t>221253</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>124530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>185511</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226133</t>
+          <t>227518</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341898</t>
+          <t>352044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138319</t>
+          <t>137940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187653</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>221746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328021</t>
+          <t>328051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>393691</t>
+          <t>395387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151549</t>
+          <t>150697</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>198891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>194750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>241405</t>
+          <t>242104</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>357754</t>
+          <t>360041</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>430345</t>
+          <t>429345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166478</t>
+          <t>168425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>219183</t>
+          <t>219358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204902</t>
+          <t>207439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343764</t>
+          <t>343175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413360</t>
+          <t>413033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos en fines de semana / solo 2023 en 2023 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos en fin de semana en 2023 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8912</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20449</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5586</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2675</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10013</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10619</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6225</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17311</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17798</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9621</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25981</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40466</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18508</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12653</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25593</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13721</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7537</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20774</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>39,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34041</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18158</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15178</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8326</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29490</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>22825</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44982</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>102936</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83410</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>128091</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>84981</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58718</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>167141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>37,24%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89017</t>
+          <t>51339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146474</t>
+          <t>76848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>198243</t>
+          <t>165356</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161836</t>
+          <t>143645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>283155</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>134668</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>118745</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153858</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>110613</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90334</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128455</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>115128</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123827</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162799</t>
+          <t>131103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>253295</t>
+          <t>249796</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222293</t>
+          <t>229383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280651</t>
+          <t>275308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130055</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>112577</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148779</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>122877</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100042</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141441</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134531</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114959</t>
+          <t>104811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155963</t>
+          <t>136770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>250635</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229494</t>
+          <t>228034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284024</t>
+          <t>277352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101479</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>117079</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>130316</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>105206</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149138</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119606</t>
+          <t>122768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102603</t>
+          <t>108875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>139346</t>
+          <t>139929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>249922</t>
+          <t>224247</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221832</t>
+          <t>204651</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275049</t>
+          <t>246134</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>469139</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>469139</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>469139</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>448787</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>448787</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>448787</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>510081</t>
+          <t>420895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510081</t>
+          <t>420895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510081</t>
+          <t>420895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>958868</t>
+          <t>890035</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>958868</t>
+          <t>890035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>958868</t>
+          <t>890035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21366</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14227</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29835</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23448</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32055</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31948</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46004</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42508</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32624</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>53358</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>19,57%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>32,01%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>34581</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>26467</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>42851</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34810</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56971</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79283</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93984</t>
+          <t>93717</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56701</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46546</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68626</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>39651</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30900</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48305</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50595</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>49606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>102417</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86844</t>
+          <t>81979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118297</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46128</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36857</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>56538</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49262</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40761</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58905</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62535</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>100741</t>
+          <t>93754</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88010</t>
+          <t>81106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117369</t>
+          <t>107750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>138329</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>116632</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>167913</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>114015</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>85897</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>221253</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>151628</t>
+          <t>92464</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>76165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>108272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>265643</t>
+          <t>230792</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>227518</t>
+          <t>204552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352044</t>
+          <t>267587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>187796</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>166155</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>210546</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>162992</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>137940</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>184852</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>197947</t>
+          <t>164975</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>147323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221746</t>
+          <t>184843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>360939</t>
+          <t>352771</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328051</t>
+          <t>323699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>395387</t>
+          <t>382416</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>205265</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>183932</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>230498</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>176249</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>150697</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>198891</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>217616</t>
+          <t>175606</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>157474</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>242104</t>
+          <t>196195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>393865</t>
+          <t>380870</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>360041</t>
+          <t>352302</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>429345</t>
+          <t>411872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>160712</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>143086</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>179366</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>194756</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>168425</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>219358</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>185818</t>
+          <t>180114</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165842</t>
+          <t>164260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207439</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>340826</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343175</t>
+          <t>315173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413033</t>
+          <t>369731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>648013</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>648013</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>648013</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613159</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1401022</t>
+          <t>1305260</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1401022</t>
+          <t>1305260</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1401022</t>
+          <t>1305260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
